--- a/artfynd/A 20785-2024 artfynd.xlsx
+++ b/artfynd/A 20785-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,215 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124979341</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Åsinget, Åsinget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>610807</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6954338</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124981558</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Åsinget, Åsinget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>610915</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6954360</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20785-2024 artfynd.xlsx
+++ b/artfynd/A 20785-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124979341</v>
+        <v>124981558</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,34 +810,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610807</v>
+        <v>610915</v>
       </c>
       <c r="R3" t="n">
-        <v>6954338</v>
+        <v>6954360</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -896,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981558</v>
+        <v>124979341</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,39 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610915</v>
+        <v>610807</v>
       </c>
       <c r="R4" t="n">
-        <v>6954360</v>
+        <v>6954338</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 20785-2024 artfynd.xlsx
+++ b/artfynd/A 20785-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981558</v>
+        <v>124979341</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,39 +810,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610915</v>
+        <v>610807</v>
       </c>
       <c r="R3" t="n">
-        <v>6954360</v>
+        <v>6954338</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -901,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124979341</v>
+        <v>124981558</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,34 +912,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610807</v>
+        <v>610915</v>
       </c>
       <c r="R4" t="n">
-        <v>6954338</v>
+        <v>6954360</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 20785-2024 artfynd.xlsx
+++ b/artfynd/A 20785-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981558</v>
+        <v>124979341</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,39 +810,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610915</v>
+        <v>610807</v>
       </c>
       <c r="R3" t="n">
-        <v>6954360</v>
+        <v>6954338</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -901,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124979341</v>
+        <v>124981558</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,34 +912,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610807</v>
+        <v>610915</v>
       </c>
       <c r="R4" t="n">
-        <v>6954338</v>
+        <v>6954360</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 20785-2024 artfynd.xlsx
+++ b/artfynd/A 20785-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124979341</v>
+        <v>124981558</v>
       </c>
       <c r="B3" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,34 +810,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610807</v>
+        <v>610915</v>
       </c>
       <c r="R3" t="n">
-        <v>6954338</v>
+        <v>6954360</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -896,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981558</v>
+        <v>124979341</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,39 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610915</v>
+        <v>610807</v>
       </c>
       <c r="R4" t="n">
-        <v>6954360</v>
+        <v>6954338</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 20785-2024 artfynd.xlsx
+++ b/artfynd/A 20785-2024 artfynd.xlsx
@@ -799,11 +799,6 @@
       <c r="B3" t="n">
         <v>57635</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>NT</t>
@@ -905,11 +900,6 @@
       </c>
       <c r="B4" t="n">
         <v>80028</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
